--- a/Fase_2/Evidencias Proyecto/Evidencias de documentación/Listo/Sprint_3_Backlog_SIGFQ_Tareas_por_HU_y_Escenarios.xlsx
+++ b/Fase_2/Evidencias Proyecto/Evidencias de documentación/Listo/Sprint_3_Backlog_SIGFQ_Tareas_por_HU_y_Escenarios.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="166">
   <si>
     <t>RESUMEN — SPRINT 3 SIGFQ</t>
   </si>
@@ -29,19 +29,115 @@
     <t>SIGFQ Sprint 3 | 05/10/2026 al 19/10/2026  | 10 días hábiles</t>
   </si>
   <si>
+    <t>Elaborado por: pmoinformatica.com</t>
+  </si>
+  <si>
+    <t>Sprint 3 | 05/10/2026 al 19/10/2026. Implementar el Punto de Venta y el comercio electrónico de SIGFQ, integrando caja, ventas, promociones, comprobantes, devoluciones, catálogo online, clientes, carrito y retiro en sucursal.</t>
+  </si>
+  <si>
+    <t>Columna</t>
+  </si>
+  <si>
     <t>Implementar el Punto de Venta y el comercio electrónico de SIGFQ, integrando caja, ventas, promociones, comprobantes, devoluciones, catálogo online, clientes, carrito y retiro en sucursal.</t>
   </si>
   <si>
-    <t>Sprint 3 | 05/10/2026 al 19/10/2026. Implementar el Punto de Venta y el comercio electrónico de SIGFQ, integrando caja, ventas, promociones, comprobantes, devoluciones, catálogo online, clientes, carrito y retiro en sucursal.</t>
-  </si>
-  <si>
-    <t>Elaborado por: pmoinformatica.com</t>
-  </si>
-  <si>
-    <t>Columna</t>
-  </si>
-  <si>
     <t>Instrucciones</t>
+  </si>
+  <si>
+    <t>Identificador (ID) de ítem de Product Backlog</t>
+  </si>
+  <si>
+    <t>Código que referencia la historia de usuario comprometida en el Sprint.</t>
+  </si>
+  <si>
+    <t>Enunciado del ítem de Product Backlog</t>
+  </si>
+  <si>
+    <t>Enunciado de la historia de usuario según la documentación vigente del proyecto SIGFQ.</t>
+  </si>
+  <si>
+    <t>Tarea</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Actividad concreta necesaria para implementar la Historia de Usuario. Debe relacionarse directamente con su funcionalidad y, cuando corresponda, con sus escenarios y criterios de aceptación; no se utilizan tareas genéricas como Análisis, Diseño, Codificación o Implementación.</t>
+  </si>
+  <si>
+    <t>Dueño / Voluntario</t>
+  </si>
+  <si>
+    <t>Integrante del Scrum Team que toma responsabilidad de la tarea.</t>
+  </si>
+  <si>
+    <t>Funcionalidad</t>
+  </si>
+  <si>
+    <t>Estatus</t>
+  </si>
+  <si>
+    <t>Estado de la tarea: Por iniciar, En proceso, Hecho o Bloqueado.</t>
+  </si>
+  <si>
+    <t>Orden lógico</t>
+  </si>
+  <si>
+    <t>Horas estimadas totales</t>
+  </si>
+  <si>
+    <t>Estado inicial</t>
+  </si>
+  <si>
+    <t>Estimación inicial de esfuerzo de la tarea; puede ser refinada por el Scrum Team.</t>
+  </si>
+  <si>
+    <t>Día 1 … Día 10</t>
+  </si>
+  <si>
+    <t>Responsable de la historia</t>
+  </si>
+  <si>
+    <t>Registro diario de horas planificadas/consumidas y saldo restante durante los 10 días hábiles del Sprint.</t>
+  </si>
+  <si>
+    <t>Cons.</t>
+  </si>
+  <si>
+    <t>Horas consumidas en la tarea durante el día.</t>
+  </si>
+  <si>
+    <t>Integrante</t>
+  </si>
+  <si>
+    <t>Rest.</t>
+  </si>
+  <si>
+    <t>Horas planificadas</t>
+  </si>
+  <si>
+    <t>Horas restantes luego del consumo del día. Se calcula automáticamente.</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Suma de horas consumidas y saldo restante de cada tarea al finalizar el Sprint.</t>
+  </si>
+  <si>
+    <t>E5-H1</t>
+  </si>
+  <si>
+    <t>Búsqueda y escaneo de productos en POS</t>
+  </si>
+  <si>
+    <t>Por iniciar</t>
+  </si>
+  <si>
+    <t>Martín Rodríguez</t>
+  </si>
+  <si>
+    <t>E5-H2</t>
   </si>
   <si>
     <t>Identificador (ID)
@@ -49,66 +145,69 @@
 Backlog</t>
   </si>
   <si>
-    <t>Identificador (ID) de ítem de Product Backlog</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Enunciado del ítem de Product Backlog</t>
-  </si>
-  <si>
-    <t>Código que referencia la historia de usuario comprometida en el Sprint.</t>
-  </si>
-  <si>
-    <t>Funcionalidad</t>
-  </si>
-  <si>
-    <t>Orden lógico</t>
-  </si>
-  <si>
-    <t>Estado inicial</t>
-  </si>
-  <si>
-    <t>Tarea</t>
-  </si>
-  <si>
-    <t>Responsable de la historia</t>
-  </si>
-  <si>
-    <t>Enunciado de la historia de usuario según la documentación vigente del proyecto SIGFQ.</t>
+    <t>Aplicación automática de promociones en POS</t>
+  </si>
+  <si>
+    <t>Jesús Lozano</t>
+  </si>
+  <si>
+    <t>E5-H5</t>
+  </si>
+  <si>
+    <t>Apertura y cierre de caja</t>
+  </si>
+  <si>
+    <t>Andrés Alvarado</t>
+  </si>
+  <si>
+    <t>E5-H3</t>
+  </si>
+  <si>
+    <t>Finalización de venta y medios de pago</t>
+  </si>
+  <si>
+    <t>E5-H4</t>
+  </si>
+  <si>
+    <t>Comprobante interno de venta</t>
+  </si>
+  <si>
+    <t>E5-H6</t>
+  </si>
+  <si>
+    <t>Anulaciones y devoluciones</t>
   </si>
   <si>
     <t>Dueño /
 Voluntario</t>
   </si>
   <si>
-    <t>Integrante</t>
-  </si>
-  <si>
-    <t>Horas planificadas</t>
-  </si>
-  <si>
-    <t>E5-H1</t>
-  </si>
-  <si>
-    <t>Estatus</t>
-  </si>
-  <si>
-    <t>Actividad concreta necesaria para implementar la Historia de Usuario. Debe relacionarse directamente con su funcionalidad y, cuando corresponda, con sus escenarios y criterios de aceptación; no se utilizan tareas genéricas como Análisis, Diseño, Codificación o Implementación.</t>
+    <t>E6-H1</t>
+  </si>
+  <si>
+    <t>Catálogo online y disponibilidad por sucursal</t>
+  </si>
+  <si>
+    <t>E6-H2</t>
+  </si>
+  <si>
+    <t>Registro e inicio de sesión de clientes</t>
+  </si>
+  <si>
+    <t>E6-H3</t>
   </si>
   <si>
     <t>Horas estimadas
 totales</t>
   </si>
   <si>
-    <t>Búsqueda y escaneo de productos en POS</t>
-  </si>
-  <si>
-    <t>Dueño / Voluntario</t>
-  </si>
-  <si>
-    <t>Por iniciar</t>
+    <t>Compra como invitado</t>
+  </si>
+  <si>
+    <t>E6-H4</t>
+  </si>
+  <si>
+    <t>Carrito online y selección de sucursal de retiro</t>
   </si>
   <si>
     <t xml:space="preserve">Día 1
@@ -116,19 +215,10 @@
 </t>
   </si>
   <si>
-    <t>Integrante del Scrum Team que toma responsabilidad de la tarea.</t>
-  </si>
-  <si>
-    <t>Martín Rodríguez</t>
-  </si>
-  <si>
-    <t>Estado de la tarea: Por iniciar, En proceso, Hecho o Bloqueado.</t>
-  </si>
-  <si>
-    <t>Horas estimadas totales</t>
-  </si>
-  <si>
-    <t>Estimación inicial de esfuerzo de la tarea; puede ser refinada por el Scrum Team.</t>
+    <t>E6-H5</t>
+  </si>
+  <si>
+    <t>Historial de pedidos online del cliente</t>
   </si>
   <si>
     <t xml:space="preserve">Día 2
@@ -136,19 +226,7 @@
 </t>
   </si>
   <si>
-    <t>E5-H2</t>
-  </si>
-  <si>
-    <t>Aplicación automática de promociones en POS</t>
-  </si>
-  <si>
-    <t>Día 1 … Día 10</t>
-  </si>
-  <si>
-    <t>Jesús Lozano</t>
-  </si>
-  <si>
-    <t>Registro diario de horas planificadas/consumidas y saldo restante durante los 10 días hábiles del Sprint.</t>
+    <t>ACUERDOS DEL SPRINT</t>
   </si>
   <si>
     <t xml:space="preserve">Día 3
@@ -156,33 +234,12 @@
 </t>
   </si>
   <si>
-    <t>E5-H5</t>
-  </si>
-  <si>
-    <t>Apertura y cierre de caja</t>
-  </si>
-  <si>
-    <t>Andrés Alvarado</t>
-  </si>
-  <si>
-    <t>E5-H3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Día 4
 Jue 08/10
 </t>
   </si>
   <si>
-    <t>Finalización de venta y medios de pago</t>
-  </si>
-  <si>
-    <t>Cons.</t>
-  </si>
-  <si>
-    <t>Horas consumidas en la tarea durante el día.</t>
-  </si>
-  <si>
-    <t>Total</t>
+    <t>Duración</t>
   </si>
   <si>
     <t xml:space="preserve">Día 5
@@ -190,16 +247,13 @@
 </t>
   </si>
   <si>
-    <t>E5-H4</t>
-  </si>
-  <si>
-    <t>Comprobante interno de venta</t>
-  </si>
-  <si>
-    <t>Rest.</t>
-  </si>
-  <si>
-    <t>Horas restantes luego del consumo del día. Se calcula automáticamente.</t>
+    <t>10 días hábiles, del 05/10/2026 al 19/10/2026.</t>
+  </si>
+  <si>
+    <t>Historias incluidas</t>
+  </si>
+  <si>
+    <t>E5-H1, E5-H2, E5-H5, E5-H3, E5-H4, E5-H6, E6-H1, E6-H2, E6-H3, E6-H4 y E6-H5.</t>
   </si>
   <si>
     <t xml:space="preserve">Día 6
@@ -207,13 +261,13 @@
 </t>
   </si>
   <si>
-    <t>E5-H6</t>
-  </si>
-  <si>
-    <t>Anulaciones y devoluciones</t>
-  </si>
-  <si>
-    <t>Suma de horas consumidas y saldo restante de cada tarea al finalizar el Sprint.</t>
+    <t>Búsqueda y escaneo en POS → promociones → apertura de caja → finalización de venta → comprobante → anulaciones/devoluciones → catálogo online → registro de clientes → compra como invitado → carrito y sucursal de retiro → historial de pedidos.</t>
+  </si>
+  <si>
+    <t>Seguimiento</t>
+  </si>
+  <si>
+    <t>Registrar diariamente las horas consumidas y restantes de cada tarea, actualizar su estado y validar cada historia mediante sus escenarios de aceptación.</t>
   </si>
   <si>
     <t xml:space="preserve">Día 7
@@ -221,10 +275,10 @@
 </t>
   </si>
   <si>
-    <t>E6-H1</t>
-  </si>
-  <si>
-    <t>Catálogo online y disponibilidad por sucursal</t>
+    <t>Estructura</t>
+  </si>
+  <si>
+    <t>Las tareas se derivan de las Historias de Usuario de las épicas E5 y E6 y consideran backend, frontend, datos, validaciones, integración y pruebas cuando corresponde.</t>
   </si>
   <si>
     <t xml:space="preserve">Día 8
@@ -232,70 +286,16 @@
 </t>
   </si>
   <si>
-    <t>E6-H2</t>
-  </si>
-  <si>
-    <t>Registro e inicio de sesión de clientes</t>
-  </si>
-  <si>
-    <t>E6-H3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Día 9
 Vie 16/10
 </t>
   </si>
   <si>
-    <t>Compra como invitado</t>
-  </si>
-  <si>
-    <t>E6-H4</t>
-  </si>
-  <si>
-    <t>Carrito online y selección de sucursal de retiro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Día 10
 Lun 19/10
 </t>
   </si>
   <si>
-    <t>E6-H5</t>
-  </si>
-  <si>
-    <t>Historial de pedidos online del cliente</t>
-  </si>
-  <si>
-    <t>ACUERDOS DEL SPRINT</t>
-  </si>
-  <si>
-    <t>Duración</t>
-  </si>
-  <si>
-    <t>10 días hábiles, del 05/10/2026 al 19/10/2026.</t>
-  </si>
-  <si>
-    <t>Historias incluidas</t>
-  </si>
-  <si>
-    <t>E5-H1, E5-H2, E5-H5, E5-H3, E5-H4, E5-H6, E6-H1, E6-H2, E6-H3, E6-H4 y E6-H5.</t>
-  </si>
-  <si>
-    <t>Búsqueda y escaneo en POS → promociones → apertura de caja → finalización de venta → comprobante → anulaciones/devoluciones → catálogo online → registro de clientes → compra como invitado → carrito y sucursal de retiro → historial de pedidos.</t>
-  </si>
-  <si>
-    <t>Seguimiento</t>
-  </si>
-  <si>
-    <t>Registrar diariamente las horas consumidas y restantes de cada tarea, actualizar su estado y validar cada historia mediante sus escenarios de aceptación.</t>
-  </si>
-  <si>
-    <t>Estructura</t>
-  </si>
-  <si>
-    <t>Las tareas se derivan de las Historias de Usuario de las épicas E5 y E6 y consideran backend, frontend, datos, validaciones, integración y pruebas cuando corresponde.</t>
-  </si>
-  <si>
     <t>Consumidas</t>
   </si>
   <si>
@@ -486,45 +486,45 @@
     <t>Registrar los datos del invitado directamente en el pedido sin crear una cuenta de cliente.</t>
   </si>
   <si>
+    <t>Asegurar que la compra como invitado no genere historial de usuario ni credenciales automáticas.</t>
+  </si>
+  <si>
+    <t>Desarrollar e integrar la opción de continuar la compra como invitado en el checkout.</t>
+  </si>
+  <si>
+    <t>Implementar y ejecutar pruebas para datos mínimos y ausencia de cuenta automática de E6-H3.</t>
+  </si>
+  <si>
+    <t>Como Cliente / Invitado, necesito gestionar el carrito y seleccionar la sucursal de retiro, con la finalidad de definir qué comprar y dónde retirar.</t>
+  </si>
+  <si>
+    <t>Implementar la gestión del carrito online para agregar, quitar y modificar cantidades de productos.</t>
+  </si>
+  <si>
+    <t>Recalcular totales y validar que los productos del carrito sean vendibles online.</t>
+  </si>
+  <si>
+    <t>Revalidar la disponibilidad global de stock al continuar al checkout.</t>
+  </si>
+  <si>
+    <t>Implementar la consulta y selección de sucursales habilitadas para retiro.</t>
+  </si>
+  <si>
+    <t>Asociar el pedido a la sucursal seleccionada aunque posteriormente requiera traslado interno de stock.</t>
+  </si>
+  <si>
+    <t>Integrar y probar el flujo completo de carrito y selección de sucursal según los escenarios de E6-H4.</t>
+  </si>
+  <si>
+    <t>Como Cliente registrado, necesito consultar el historial de mis pedidos online, con la finalidad de revisar estados y compras anteriores.</t>
+  </si>
+  <si>
+    <t>Implementar en backend la consulta de pedidos online del cliente autenticado.</t>
+  </si>
+  <si>
     <t>Bloqueado</t>
   </si>
   <si>
-    <t>Asegurar que la compra como invitado no genere historial de usuario ni credenciales automáticas.</t>
-  </si>
-  <si>
-    <t>Desarrollar e integrar la opción de continuar la compra como invitado en el checkout.</t>
-  </si>
-  <si>
-    <t>Implementar y ejecutar pruebas para datos mínimos y ausencia de cuenta automática de E6-H3.</t>
-  </si>
-  <si>
-    <t>Como Cliente / Invitado, necesito gestionar el carrito y seleccionar la sucursal de retiro, con la finalidad de definir qué comprar y dónde retirar.</t>
-  </si>
-  <si>
-    <t>Implementar la gestión del carrito online para agregar, quitar y modificar cantidades de productos.</t>
-  </si>
-  <si>
-    <t>Recalcular totales y validar que los productos del carrito sean vendibles online.</t>
-  </si>
-  <si>
-    <t>Revalidar la disponibilidad global de stock al continuar al checkout.</t>
-  </si>
-  <si>
-    <t>Implementar la consulta y selección de sucursales habilitadas para retiro.</t>
-  </si>
-  <si>
-    <t>Asociar el pedido a la sucursal seleccionada aunque posteriormente requiera traslado interno de stock.</t>
-  </si>
-  <si>
-    <t>Integrar y probar el flujo completo de carrito y selección de sucursal según los escenarios de E6-H4.</t>
-  </si>
-  <si>
-    <t>Como Cliente registrado, necesito consultar el historial de mis pedidos online, con la finalidad de revisar estados y compras anteriores.</t>
-  </si>
-  <si>
-    <t>Implementar en backend la consulta de pedidos online del cliente autenticado.</t>
-  </si>
-  <si>
     <t>Filtrar la consulta para mostrar únicamente los pedidos pertenecientes al cliente que inició sesión.</t>
   </si>
   <si>
@@ -535,9 +535,6 @@
   </si>
   <si>
     <t>Desarrollar e integrar la interfaz de Mis pedidos para el cliente registrado.</t>
-  </si>
-  <si>
-    <t>En proceso</t>
   </si>
   <si>
     <t>Implementar y ejecutar pruebas de autenticación, pertenencia y exclusión de ventas POS para E6-H5.</t>
@@ -559,20 +556,14 @@
     </font>
     <font>
       <b/>
-      <sz val="22.0"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
       <sz val="20.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="22.0"/>
+      <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
     <font/>
@@ -584,17 +575,34 @@
     </font>
     <font>
       <b/>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11.0"/>
       <color rgb="FF244A7C"/>
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
     <font>
       <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
@@ -605,26 +613,15 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <b/>
       <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
+      <color theme="1"/>
+      <name val="Quattrocento Sans"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Quattrocento Sans"/>
     </font>
     <font>
       <b/>
@@ -681,14 +678,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF1F4E78"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -723,12 +720,23 @@
       <top/>
     </border>
     <border>
+      <top/>
+    </border>
+    <border>
+      <right/>
+      <top/>
+    </border>
+    <border>
       <left/>
       <top/>
       <bottom/>
     </border>
     <border>
-      <top/>
+      <left/>
+      <bottom/>
+    </border>
+    <border>
+      <bottom/>
     </border>
     <border>
       <top/>
@@ -737,17 +745,6 @@
     <border>
       <right/>
       <top/>
-    </border>
-    <border>
-      <left/>
-      <bottom/>
-    </border>
-    <border>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
       <bottom/>
     </border>
     <border>
@@ -781,93 +778,93 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="10" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="11" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="4" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="4" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -893,7 +890,7 @@
     <xf borderId="0" fillId="0" fontId="17" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="6" fontId="18" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
@@ -943,7 +940,7 @@
     <xf borderId="10" fillId="8" fontId="18" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1196,227 +1193,227 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="G1" s="3" t="s">
+      <c r="A1" s="2"/>
+      <c r="G1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="8"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="10"/>
     </row>
     <row r="2" ht="27.75" customHeight="1">
-      <c r="G2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="6"/>
+      <c r="G2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="4"/>
     </row>
     <row r="3" ht="21.75" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="10"/>
+      <c r="A3" s="20"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="T4" s="5"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="W4" s="5"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="25" t="s">
+      <c r="A4" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="9"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="8"/>
-      <c r="AH4" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI4" s="8"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL4" s="8"/>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" s="9"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="W4" s="9"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="31"/>
+      <c r="AK4" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL4" s="10"/>
+      <c r="AM4" s="33"/>
+      <c r="AN4" s="33"/>
+      <c r="AO4" s="33"/>
+      <c r="AP4" s="33"/>
     </row>
     <row r="5" ht="33.75" customHeight="1">
-      <c r="A5" s="31"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="L5" s="35"/>
-      <c r="M5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" s="35"/>
-      <c r="P5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="R5" s="35"/>
-      <c r="S5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="T5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="U5" s="35"/>
-      <c r="V5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="W5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD5" s="35"/>
-      <c r="AE5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG5" s="35"/>
-      <c r="AH5" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI5" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ5" s="35"/>
-      <c r="AK5" s="33" t="s">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="36"/>
+      <c r="J5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="36"/>
+      <c r="M5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="36"/>
+      <c r="P5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" s="36"/>
+      <c r="S5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="U5" s="36"/>
+      <c r="V5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA5" s="36"/>
+      <c r="AB5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD5" s="36"/>
+      <c r="AE5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG5" s="36"/>
+      <c r="AH5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ5" s="36"/>
+      <c r="AK5" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="AL5" s="33" t="s">
+      <c r="AL5" s="35" t="s">
         <v>85</v>
       </c>
       <c r="AM5" s="37"/>
@@ -1426,7 +1423,7 @@
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="38" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B6" s="39" t="s">
         <v>86</v>
@@ -1435,7 +1432,7 @@
         <v>87</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E6" s="41" t="s">
         <v>88</v>
@@ -1533,7 +1530,7 @@
         <v>89</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E7" s="41" t="s">
         <v>88</v>
@@ -1631,7 +1628,7 @@
         <v>90</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E8" s="41" t="s">
         <v>88</v>
@@ -1729,7 +1726,7 @@
         <v>91</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E9" s="41" t="s">
         <v>88</v>
@@ -1827,7 +1824,7 @@
         <v>92</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E10" s="41" t="s">
         <v>88</v>
@@ -1919,13 +1916,13 @@
       <c r="AP10" s="44"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
       <c r="C11" s="40" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E11" s="41" t="s">
         <v>88</v>
@@ -2018,7 +2015,7 @@
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="47" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B12" s="48" t="s">
         <v>94</v>
@@ -2027,7 +2024,7 @@
         <v>95</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>88</v>
@@ -2125,7 +2122,7 @@
         <v>96</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E13" s="50" t="s">
         <v>88</v>
@@ -2223,7 +2220,7 @@
         <v>97</v>
       </c>
       <c r="D14" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E14" s="50" t="s">
         <v>88</v>
@@ -2321,7 +2318,7 @@
         <v>98</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E15" s="50" t="s">
         <v>88</v>
@@ -2419,7 +2416,7 @@
         <v>99</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E16" s="50" t="s">
         <v>88</v>
@@ -2511,13 +2508,13 @@
       <c r="AP16" s="44"/>
     </row>
     <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="49" t="s">
         <v>100</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E17" s="50" t="s">
         <v>88</v>
@@ -2610,7 +2607,7 @@
     </row>
     <row r="18" ht="42.0" customHeight="1">
       <c r="A18" s="52" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="39" t="s">
         <v>101</v>
@@ -2619,7 +2616,7 @@
         <v>102</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E18" s="41" t="s">
         <v>88</v>
@@ -2717,7 +2714,7 @@
         <v>103</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E19" s="41" t="s">
         <v>88</v>
@@ -2815,7 +2812,7 @@
         <v>104</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E20" s="41" t="s">
         <v>88</v>
@@ -2913,7 +2910,7 @@
         <v>105</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21" s="41" t="s">
         <v>88</v>
@@ -3011,7 +3008,7 @@
         <v>106</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E22" s="41" t="s">
         <v>88</v>
@@ -3103,13 +3100,13 @@
       <c r="AP22" s="44"/>
     </row>
     <row r="23" ht="42.0" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
       <c r="C23" s="40" t="s">
         <v>107</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E23" s="41" t="s">
         <v>88</v>
@@ -3202,7 +3199,7 @@
     </row>
     <row r="24" ht="42.0" customHeight="1">
       <c r="A24" s="47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="48" t="s">
         <v>108</v>
@@ -3211,7 +3208,7 @@
         <v>109</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E24" s="50" t="s">
         <v>88</v>
@@ -3309,7 +3306,7 @@
         <v>110</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" s="50" t="s">
         <v>88</v>
@@ -3407,7 +3404,7 @@
         <v>111</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E26" s="50" t="s">
         <v>88</v>
@@ -3505,7 +3502,7 @@
         <v>112</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E27" s="50" t="s">
         <v>88</v>
@@ -3603,7 +3600,7 @@
         <v>113</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28" s="50" t="s">
         <v>88</v>
@@ -3695,13 +3692,13 @@
       <c r="AP28" s="44"/>
     </row>
     <row r="29" ht="42.0" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="49" t="s">
         <v>114</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E29" s="50" t="s">
         <v>88</v>
@@ -3794,7 +3791,7 @@
     </row>
     <row r="30" ht="42.0" customHeight="1">
       <c r="A30" s="52" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B30" s="39" t="s">
         <v>115</v>
@@ -3803,7 +3800,7 @@
         <v>116</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30" s="56" t="s">
         <v>88</v>
@@ -3901,7 +3898,7 @@
         <v>117</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E31" s="56" t="s">
         <v>88</v>
@@ -3999,7 +3996,7 @@
         <v>118</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E32" s="56" t="s">
         <v>88</v>
@@ -4097,7 +4094,7 @@
         <v>119</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E33" s="56" t="s">
         <v>88</v>
@@ -4195,7 +4192,7 @@
         <v>120</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E34" s="56" t="s">
         <v>88</v>
@@ -4287,13 +4284,13 @@
       <c r="AP34" s="44"/>
     </row>
     <row r="35" ht="42.0" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
       <c r="C35" s="40" t="s">
         <v>121</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E35" s="56" t="s">
         <v>88</v>
@@ -4386,7 +4383,7 @@
     </row>
     <row r="36" ht="42.0" customHeight="1">
       <c r="A36" s="47" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B36" s="48" t="s">
         <v>122</v>
@@ -4395,7 +4392,7 @@
         <v>123</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E36" s="58" t="s">
         <v>88</v>
@@ -4493,7 +4490,7 @@
         <v>124</v>
       </c>
       <c r="D37" s="50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E37" s="58" t="s">
         <v>88</v>
@@ -4591,7 +4588,7 @@
         <v>125</v>
       </c>
       <c r="D38" s="50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E38" s="58" t="s">
         <v>88</v>
@@ -4689,7 +4686,7 @@
         <v>126</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E39" s="58" t="s">
         <v>88</v>
@@ -4787,7 +4784,7 @@
         <v>127</v>
       </c>
       <c r="D40" s="50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E40" s="58" t="s">
         <v>88</v>
@@ -4879,13 +4876,13 @@
       <c r="AP40" s="44"/>
     </row>
     <row r="41" ht="42.0" customHeight="1">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
       <c r="C41" s="49" t="s">
         <v>128</v>
       </c>
       <c r="D41" s="50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E41" s="58" t="s">
         <v>88</v>
@@ -4978,7 +4975,7 @@
     </row>
     <row r="42" ht="42.0" customHeight="1">
       <c r="A42" s="52" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B42" s="39" t="s">
         <v>129</v>
@@ -4987,7 +4984,7 @@
         <v>130</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E42" s="56" t="s">
         <v>88</v>
@@ -5085,7 +5082,7 @@
         <v>131</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E43" s="56" t="s">
         <v>88</v>
@@ -5183,7 +5180,7 @@
         <v>132</v>
       </c>
       <c r="D44" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E44" s="56" t="s">
         <v>88</v>
@@ -5281,7 +5278,7 @@
         <v>133</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E45" s="56" t="s">
         <v>88</v>
@@ -5379,7 +5376,7 @@
         <v>134</v>
       </c>
       <c r="D46" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E46" s="56" t="s">
         <v>88</v>
@@ -5471,13 +5468,13 @@
       <c r="AP46" s="44"/>
     </row>
     <row r="47" ht="42.0" customHeight="1">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
       <c r="C47" s="40" t="s">
         <v>135</v>
       </c>
       <c r="D47" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E47" s="56" t="s">
         <v>88</v>
@@ -5570,7 +5567,7 @@
     </row>
     <row r="48" ht="42.0" customHeight="1">
       <c r="A48" s="47" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B48" s="48" t="s">
         <v>136</v>
@@ -5579,7 +5576,7 @@
         <v>137</v>
       </c>
       <c r="D48" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E48" s="58" t="s">
         <v>88</v>
@@ -5677,7 +5674,7 @@
         <v>138</v>
       </c>
       <c r="D49" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49" s="58" t="s">
         <v>88</v>
@@ -5775,7 +5772,7 @@
         <v>139</v>
       </c>
       <c r="D50" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E50" s="58" t="s">
         <v>88</v>
@@ -5873,7 +5870,7 @@
         <v>140</v>
       </c>
       <c r="D51" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E51" s="58" t="s">
         <v>88</v>
@@ -5971,7 +5968,7 @@
         <v>141</v>
       </c>
       <c r="D52" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E52" s="58" t="s">
         <v>88</v>
@@ -6063,13 +6060,13 @@
       <c r="AP52" s="44"/>
     </row>
     <row r="53" ht="42.0" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
       <c r="C53" s="49" t="s">
         <v>142</v>
       </c>
       <c r="D53" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E53" s="58" t="s">
         <v>88</v>
@@ -6162,7 +6159,7 @@
     </row>
     <row r="54" ht="42.0" customHeight="1">
       <c r="A54" s="52" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B54" s="39" t="s">
         <v>143</v>
@@ -6171,7 +6168,7 @@
         <v>144</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E54" s="41" t="s">
         <v>88</v>
@@ -6269,7 +6266,7 @@
         <v>145</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E55" s="41" t="s">
         <v>88</v>
@@ -6367,10 +6364,10 @@
         <v>146</v>
       </c>
       <c r="D56" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E56" s="41" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="F56" s="42">
         <v>2.0</v>
@@ -6462,10 +6459,10 @@
       <c r="A57" s="45"/>
       <c r="B57" s="45"/>
       <c r="C57" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E57" s="41" t="s">
         <v>88</v>
@@ -6560,10 +6557,10 @@
       <c r="A58" s="45"/>
       <c r="B58" s="45"/>
       <c r="C58" s="40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D58" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E58" s="41" t="s">
         <v>88</v>
@@ -6655,13 +6652,13 @@
       <c r="AP58" s="44"/>
     </row>
     <row r="59" ht="42.0" customHeight="1">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
       <c r="C59" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D59" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E59" s="41" t="s">
         <v>88</v>
@@ -6754,16 +6751,16 @@
     </row>
     <row r="60" ht="42.0" customHeight="1">
       <c r="A60" s="47" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B60" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="C60" s="49" t="s">
-        <v>152</v>
-      </c>
       <c r="D60" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E60" s="50" t="s">
         <v>88</v>
@@ -6858,10 +6855,10 @@
       <c r="A61" s="45"/>
       <c r="B61" s="45"/>
       <c r="C61" s="49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D61" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E61" s="50" t="s">
         <v>88</v>
@@ -6956,10 +6953,10 @@
       <c r="A62" s="45"/>
       <c r="B62" s="45"/>
       <c r="C62" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D62" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E62" s="50" t="s">
         <v>88</v>
@@ -7054,10 +7051,10 @@
       <c r="A63" s="45"/>
       <c r="B63" s="45"/>
       <c r="C63" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E63" s="50" t="s">
         <v>88</v>
@@ -7152,10 +7149,10 @@
       <c r="A64" s="45"/>
       <c r="B64" s="45"/>
       <c r="C64" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D64" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E64" s="50" t="s">
         <v>88</v>
@@ -7247,13 +7244,13 @@
       <c r="AP64" s="44"/>
     </row>
     <row r="65" ht="42.0" customHeight="1">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
       <c r="C65" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D65" s="50" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E65" s="50" t="s">
         <v>88</v>
@@ -7346,19 +7343,19 @@
     </row>
     <row r="66" ht="42.0" customHeight="1">
       <c r="A66" s="52" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B66" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="C66" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="C66" s="40" t="s">
+      <c r="D66" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E66" s="41" t="s">
         <v>159</v>
-      </c>
-      <c r="D66" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="E66" s="41" t="s">
-        <v>147</v>
       </c>
       <c r="F66" s="42">
         <v>1.0</v>
@@ -7453,10 +7450,10 @@
         <v>160</v>
       </c>
       <c r="D67" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E67" s="41" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F67" s="42">
         <v>1.0</v>
@@ -7551,10 +7548,10 @@
         <v>161</v>
       </c>
       <c r="D68" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E68" s="41" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F68" s="42">
         <v>2.0</v>
@@ -7649,10 +7646,10 @@
         <v>162</v>
       </c>
       <c r="D69" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E69" s="41" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F69" s="42">
         <v>1.0</v>
@@ -7747,10 +7744,10 @@
         <v>163</v>
       </c>
       <c r="D70" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E70" s="41" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F70" s="42">
         <v>1.0</v>
@@ -7839,16 +7836,16 @@
       <c r="AP70" s="44"/>
     </row>
     <row r="71" ht="42.0" customHeight="1">
-      <c r="A71" s="10"/>
-      <c r="B71" s="10"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
       <c r="C71" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D71" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E71" s="41" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F71" s="42">
         <v>1.0</v>
@@ -7938,7 +7935,7 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="59" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B72" s="59"/>
       <c r="C72" s="60"/>
@@ -8053,803 +8050,803 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="B73" s="63"/>
-      <c r="C73" s="26"/>
+      <c r="C73" s="23"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="B74" s="63"/>
-      <c r="C74" s="26"/>
+      <c r="C74" s="23"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="63"/>
-      <c r="C75" s="26"/>
+      <c r="C75" s="23"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="B76" s="63"/>
-      <c r="C76" s="26"/>
+      <c r="C76" s="23"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="B77" s="63"/>
-      <c r="C77" s="26"/>
+      <c r="C77" s="23"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="63"/>
-      <c r="C78" s="26"/>
+      <c r="C78" s="23"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="63"/>
-      <c r="C79" s="26"/>
+      <c r="C79" s="23"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="63"/>
-      <c r="C80" s="26"/>
+      <c r="C80" s="23"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="63"/>
-      <c r="C81" s="26"/>
+      <c r="C81" s="23"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="63"/>
-      <c r="C82" s="26"/>
+      <c r="C82" s="23"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="63"/>
-      <c r="C83" s="26"/>
+      <c r="C83" s="23"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="63"/>
-      <c r="C84" s="26"/>
+      <c r="C84" s="23"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="B85" s="63"/>
-      <c r="C85" s="26"/>
+      <c r="C85" s="23"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="B86" s="63"/>
-      <c r="C86" s="26"/>
+      <c r="C86" s="23"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="63"/>
-      <c r="C87" s="26"/>
+      <c r="C87" s="23"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="B88" s="63"/>
-      <c r="C88" s="26"/>
+      <c r="C88" s="23"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="B89" s="63"/>
-      <c r="C89" s="26"/>
+      <c r="C89" s="23"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="B90" s="63"/>
-      <c r="C90" s="26"/>
+      <c r="C90" s="23"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="B91" s="63"/>
-      <c r="C91" s="26"/>
+      <c r="C91" s="23"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="B92" s="63"/>
-      <c r="C92" s="26"/>
+      <c r="C92" s="23"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="B93" s="63"/>
-      <c r="C93" s="26"/>
+      <c r="C93" s="23"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="B94" s="63"/>
-      <c r="C94" s="26"/>
+      <c r="C94" s="23"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="B95" s="63"/>
-      <c r="C95" s="26"/>
+      <c r="C95" s="23"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="B96" s="63"/>
-      <c r="C96" s="26"/>
+      <c r="C96" s="23"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="B97" s="63"/>
-      <c r="C97" s="26"/>
+      <c r="C97" s="23"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="B98" s="63"/>
-      <c r="C98" s="26"/>
+      <c r="C98" s="23"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="63"/>
-      <c r="C99" s="26"/>
+      <c r="C99" s="23"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="63"/>
-      <c r="C100" s="26"/>
+      <c r="C100" s="23"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="63"/>
-      <c r="C101" s="26"/>
+      <c r="C101" s="23"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="B102" s="63"/>
-      <c r="C102" s="26"/>
+      <c r="C102" s="23"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="B103" s="63"/>
-      <c r="C103" s="26"/>
+      <c r="C103" s="23"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="B104" s="63"/>
-      <c r="C104" s="26"/>
+      <c r="C104" s="23"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="B105" s="63"/>
-      <c r="C105" s="26"/>
+      <c r="C105" s="23"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="B106" s="63"/>
-      <c r="C106" s="26"/>
+      <c r="C106" s="23"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="B107" s="63"/>
-      <c r="C107" s="26"/>
+      <c r="C107" s="23"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="63"/>
-      <c r="C108" s="26"/>
+      <c r="C108" s="23"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="B109" s="63"/>
-      <c r="C109" s="26"/>
+      <c r="C109" s="23"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="B110" s="63"/>
-      <c r="C110" s="26"/>
+      <c r="C110" s="23"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="B111" s="63"/>
-      <c r="C111" s="26"/>
+      <c r="C111" s="23"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="B112" s="63"/>
-      <c r="C112" s="26"/>
+      <c r="C112" s="23"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="63"/>
-      <c r="C113" s="26"/>
+      <c r="C113" s="23"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="63"/>
-      <c r="C114" s="26"/>
+      <c r="C114" s="23"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="B115" s="63"/>
-      <c r="C115" s="26"/>
+      <c r="C115" s="23"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="B116" s="63"/>
-      <c r="C116" s="26"/>
+      <c r="C116" s="23"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="B117" s="63"/>
-      <c r="C117" s="26"/>
+      <c r="C117" s="23"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="B118" s="63"/>
-      <c r="C118" s="26"/>
+      <c r="C118" s="23"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="B119" s="63"/>
-      <c r="C119" s="26"/>
+      <c r="C119" s="23"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="B120" s="63"/>
-      <c r="C120" s="26"/>
+      <c r="C120" s="23"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="B121" s="63"/>
-      <c r="C121" s="26"/>
+      <c r="C121" s="23"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="B122" s="63"/>
-      <c r="C122" s="26"/>
+      <c r="C122" s="23"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="B123" s="63"/>
-      <c r="C123" s="26"/>
+      <c r="C123" s="23"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="B124" s="63"/>
-      <c r="C124" s="26"/>
+      <c r="C124" s="23"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="B125" s="63"/>
-      <c r="C125" s="26"/>
+      <c r="C125" s="23"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="B126" s="63"/>
-      <c r="C126" s="26"/>
+      <c r="C126" s="23"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="B127" s="63"/>
-      <c r="C127" s="26"/>
+      <c r="C127" s="23"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="B128" s="63"/>
-      <c r="C128" s="26"/>
+      <c r="C128" s="23"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="B129" s="63"/>
-      <c r="C129" s="26"/>
+      <c r="C129" s="23"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="B130" s="63"/>
-      <c r="C130" s="26"/>
+      <c r="C130" s="23"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="B131" s="63"/>
-      <c r="C131" s="26"/>
+      <c r="C131" s="23"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="B132" s="63"/>
-      <c r="C132" s="26"/>
+      <c r="C132" s="23"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="B133" s="63"/>
-      <c r="C133" s="26"/>
+      <c r="C133" s="23"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="B134" s="63"/>
-      <c r="C134" s="26"/>
+      <c r="C134" s="23"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="63"/>
-      <c r="C135" s="26"/>
+      <c r="C135" s="23"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="B136" s="63"/>
-      <c r="C136" s="26"/>
+      <c r="C136" s="23"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="B137" s="63"/>
-      <c r="C137" s="26"/>
+      <c r="C137" s="23"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="B138" s="63"/>
-      <c r="C138" s="26"/>
+      <c r="C138" s="23"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="B139" s="63"/>
-      <c r="C139" s="26"/>
+      <c r="C139" s="23"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="B140" s="63"/>
-      <c r="C140" s="26"/>
+      <c r="C140" s="23"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="B141" s="63"/>
-      <c r="C141" s="26"/>
+      <c r="C141" s="23"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="B142" s="63"/>
-      <c r="C142" s="26"/>
+      <c r="C142" s="23"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="B143" s="63"/>
-      <c r="C143" s="26"/>
+      <c r="C143" s="23"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="B144" s="63"/>
-      <c r="C144" s="26"/>
+      <c r="C144" s="23"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="B145" s="63"/>
-      <c r="C145" s="26"/>
+      <c r="C145" s="23"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="B146" s="63"/>
-      <c r="C146" s="26"/>
+      <c r="C146" s="23"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="B147" s="63"/>
-      <c r="C147" s="26"/>
+      <c r="C147" s="23"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="B148" s="63"/>
-      <c r="C148" s="26"/>
+      <c r="C148" s="23"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="B149" s="63"/>
-      <c r="C149" s="26"/>
+      <c r="C149" s="23"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="B150" s="63"/>
-      <c r="C150" s="26"/>
+      <c r="C150" s="23"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="B151" s="63"/>
-      <c r="C151" s="26"/>
+      <c r="C151" s="23"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="B152" s="63"/>
-      <c r="C152" s="26"/>
+      <c r="C152" s="23"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="B153" s="63"/>
-      <c r="C153" s="26"/>
+      <c r="C153" s="23"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="B154" s="63"/>
-      <c r="C154" s="26"/>
+      <c r="C154" s="23"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="B155" s="63"/>
-      <c r="C155" s="26"/>
+      <c r="C155" s="23"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="B156" s="63"/>
-      <c r="C156" s="26"/>
+      <c r="C156" s="23"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="B157" s="63"/>
-      <c r="C157" s="26"/>
+      <c r="C157" s="23"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="B158" s="63"/>
-      <c r="C158" s="26"/>
+      <c r="C158" s="23"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="B159" s="63"/>
-      <c r="C159" s="26"/>
+      <c r="C159" s="23"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="B160" s="63"/>
-      <c r="C160" s="26"/>
+      <c r="C160" s="23"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="B161" s="63"/>
-      <c r="C161" s="26"/>
+      <c r="C161" s="23"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="B162" s="63"/>
-      <c r="C162" s="26"/>
+      <c r="C162" s="23"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="B163" s="63"/>
-      <c r="C163" s="26"/>
+      <c r="C163" s="23"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="B164" s="63"/>
-      <c r="C164" s="26"/>
+      <c r="C164" s="23"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="B165" s="63"/>
-      <c r="C165" s="26"/>
+      <c r="C165" s="23"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="B166" s="63"/>
-      <c r="C166" s="26"/>
+      <c r="C166" s="23"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="B167" s="63"/>
-      <c r="C167" s="26"/>
+      <c r="C167" s="23"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="B168" s="63"/>
-      <c r="C168" s="26"/>
+      <c r="C168" s="23"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="B169" s="63"/>
-      <c r="C169" s="26"/>
+      <c r="C169" s="23"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="B170" s="63"/>
-      <c r="C170" s="26"/>
+      <c r="C170" s="23"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="B171" s="63"/>
-      <c r="C171" s="26"/>
+      <c r="C171" s="23"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="B172" s="63"/>
-      <c r="C172" s="26"/>
+      <c r="C172" s="23"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="B173" s="63"/>
-      <c r="C173" s="26"/>
+      <c r="C173" s="23"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="B174" s="63"/>
-      <c r="C174" s="26"/>
+      <c r="C174" s="23"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="B175" s="63"/>
-      <c r="C175" s="26"/>
+      <c r="C175" s="23"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="B176" s="63"/>
-      <c r="C176" s="26"/>
+      <c r="C176" s="23"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="B177" s="63"/>
-      <c r="C177" s="26"/>
+      <c r="C177" s="23"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="B178" s="63"/>
-      <c r="C178" s="26"/>
+      <c r="C178" s="23"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="B179" s="63"/>
-      <c r="C179" s="26"/>
+      <c r="C179" s="23"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="B180" s="63"/>
-      <c r="C180" s="26"/>
+      <c r="C180" s="23"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="B181" s="63"/>
-      <c r="C181" s="26"/>
+      <c r="C181" s="23"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="B182" s="63"/>
-      <c r="C182" s="26"/>
+      <c r="C182" s="23"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="B183" s="63"/>
-      <c r="C183" s="26"/>
+      <c r="C183" s="23"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="B184" s="63"/>
-      <c r="C184" s="26"/>
+      <c r="C184" s="23"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="B185" s="63"/>
-      <c r="C185" s="26"/>
+      <c r="C185" s="23"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="B186" s="63"/>
-      <c r="C186" s="26"/>
+      <c r="C186" s="23"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="B187" s="63"/>
-      <c r="C187" s="26"/>
+      <c r="C187" s="23"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="B188" s="63"/>
-      <c r="C188" s="26"/>
+      <c r="C188" s="23"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="B189" s="63"/>
-      <c r="C189" s="26"/>
+      <c r="C189" s="23"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="B190" s="63"/>
-      <c r="C190" s="26"/>
+      <c r="C190" s="23"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="B191" s="63"/>
-      <c r="C191" s="26"/>
+      <c r="C191" s="23"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="B192" s="63"/>
-      <c r="C192" s="26"/>
+      <c r="C192" s="23"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="B193" s="63"/>
-      <c r="C193" s="26"/>
+      <c r="C193" s="23"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="B194" s="63"/>
-      <c r="C194" s="26"/>
+      <c r="C194" s="23"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="B195" s="63"/>
-      <c r="C195" s="26"/>
+      <c r="C195" s="23"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="B196" s="63"/>
-      <c r="C196" s="26"/>
+      <c r="C196" s="23"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="B197" s="63"/>
-      <c r="C197" s="26"/>
+      <c r="C197" s="23"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="B198" s="63"/>
-      <c r="C198" s="26"/>
+      <c r="C198" s="23"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="B199" s="63"/>
-      <c r="C199" s="26"/>
+      <c r="C199" s="23"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="B200" s="63"/>
-      <c r="C200" s="26"/>
+      <c r="C200" s="23"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="B201" s="63"/>
-      <c r="C201" s="26"/>
+      <c r="C201" s="23"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="B202" s="63"/>
-      <c r="C202" s="26"/>
+      <c r="C202" s="23"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="B203" s="63"/>
-      <c r="C203" s="26"/>
+      <c r="C203" s="23"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="B204" s="63"/>
-      <c r="C204" s="26"/>
+      <c r="C204" s="23"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="B205" s="63"/>
-      <c r="C205" s="26"/>
+      <c r="C205" s="23"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="B206" s="63"/>
-      <c r="C206" s="26"/>
+      <c r="C206" s="23"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="B207" s="63"/>
-      <c r="C207" s="26"/>
+      <c r="C207" s="23"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="B208" s="63"/>
-      <c r="C208" s="26"/>
+      <c r="C208" s="23"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="B209" s="63"/>
-      <c r="C209" s="26"/>
+      <c r="C209" s="23"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="B210" s="63"/>
-      <c r="C210" s="26"/>
+      <c r="C210" s="23"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="B211" s="63"/>
-      <c r="C211" s="26"/>
+      <c r="C211" s="23"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="B212" s="63"/>
-      <c r="C212" s="26"/>
+      <c r="C212" s="23"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="B213" s="63"/>
-      <c r="C213" s="26"/>
+      <c r="C213" s="23"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="B214" s="63"/>
-      <c r="C214" s="26"/>
+      <c r="C214" s="23"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="B215" s="63"/>
-      <c r="C215" s="26"/>
+      <c r="C215" s="23"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="B216" s="63"/>
-      <c r="C216" s="26"/>
+      <c r="C216" s="23"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="B217" s="63"/>
-      <c r="C217" s="26"/>
+      <c r="C217" s="23"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="B218" s="63"/>
-      <c r="C218" s="26"/>
+      <c r="C218" s="23"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="B219" s="63"/>
-      <c r="C219" s="26"/>
+      <c r="C219" s="23"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="B220" s="63"/>
-      <c r="C220" s="26"/>
+      <c r="C220" s="23"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="B221" s="63"/>
-      <c r="C221" s="26"/>
+      <c r="C221" s="23"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="B222" s="63"/>
-      <c r="C222" s="26"/>
+      <c r="C222" s="23"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="B223" s="63"/>
-      <c r="C223" s="26"/>
+      <c r="C223" s="23"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="B224" s="63"/>
-      <c r="C224" s="26"/>
+      <c r="C224" s="23"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="B225" s="63"/>
-      <c r="C225" s="26"/>
+      <c r="C225" s="23"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="B226" s="63"/>
-      <c r="C226" s="26"/>
+      <c r="C226" s="23"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="B227" s="63"/>
-      <c r="C227" s="26"/>
+      <c r="C227" s="23"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="B228" s="63"/>
-      <c r="C228" s="26"/>
+      <c r="C228" s="23"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="B229" s="63"/>
-      <c r="C229" s="26"/>
+      <c r="C229" s="23"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="B230" s="63"/>
-      <c r="C230" s="26"/>
+      <c r="C230" s="23"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="B231" s="63"/>
-      <c r="C231" s="26"/>
+      <c r="C231" s="23"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="B232" s="63"/>
-      <c r="C232" s="26"/>
+      <c r="C232" s="23"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="B233" s="63"/>
-      <c r="C233" s="26"/>
+      <c r="C233" s="23"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="B234" s="63"/>
-      <c r="C234" s="26"/>
+      <c r="C234" s="23"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="B235" s="63"/>
-      <c r="C235" s="26"/>
+      <c r="C235" s="23"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="B236" s="63"/>
-      <c r="C236" s="26"/>
+      <c r="C236" s="23"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="B237" s="63"/>
-      <c r="C237" s="26"/>
+      <c r="C237" s="23"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="B238" s="63"/>
-      <c r="C238" s="26"/>
+      <c r="C238" s="23"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="B239" s="63"/>
-      <c r="C239" s="26"/>
+      <c r="C239" s="23"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="B240" s="63"/>
-      <c r="C240" s="26"/>
+      <c r="C240" s="23"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="B241" s="63"/>
-      <c r="C241" s="26"/>
+      <c r="C241" s="23"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="B242" s="63"/>
-      <c r="C242" s="26"/>
+      <c r="C242" s="23"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="B243" s="63"/>
-      <c r="C243" s="26"/>
+      <c r="C243" s="23"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="B244" s="63"/>
-      <c r="C244" s="26"/>
+      <c r="C244" s="23"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="B245" s="63"/>
-      <c r="C245" s="26"/>
+      <c r="C245" s="23"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="B246" s="63"/>
-      <c r="C246" s="26"/>
+      <c r="C246" s="23"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="B247" s="63"/>
-      <c r="C247" s="26"/>
+      <c r="C247" s="23"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="B248" s="63"/>
-      <c r="C248" s="26"/>
+      <c r="C248" s="23"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="B249" s="63"/>
-      <c r="C249" s="26"/>
+      <c r="C249" s="23"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="B250" s="63"/>
-      <c r="C250" s="26"/>
+      <c r="C250" s="23"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="B251" s="63"/>
-      <c r="C251" s="26"/>
+      <c r="C251" s="23"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="B252" s="63"/>
-      <c r="C252" s="26"/>
+      <c r="C252" s="23"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="B253" s="63"/>
-      <c r="C253" s="26"/>
+      <c r="C253" s="23"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="B254" s="63"/>
-      <c r="C254" s="26"/>
+      <c r="C254" s="23"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="B255" s="63"/>
-      <c r="C255" s="26"/>
+      <c r="C255" s="23"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="B256" s="63"/>
-      <c r="C256" s="26"/>
+      <c r="C256" s="23"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="B257" s="63"/>
-      <c r="C257" s="26"/>
+      <c r="C257" s="23"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="B258" s="63"/>
-      <c r="C258" s="26"/>
+      <c r="C258" s="23"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="B259" s="63"/>
-      <c r="C259" s="26"/>
+      <c r="C259" s="23"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="B260" s="63"/>
-      <c r="C260" s="26"/>
+      <c r="C260" s="23"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="B261" s="63"/>
-      <c r="C261" s="26"/>
+      <c r="C261" s="23"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="B262" s="63"/>
-      <c r="C262" s="26"/>
+      <c r="C262" s="23"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="B263" s="63"/>
-      <c r="C263" s="26"/>
+      <c r="C263" s="23"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="B264" s="63"/>
-      <c r="C264" s="26"/>
+      <c r="C264" s="23"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="B265" s="63"/>
-      <c r="C265" s="26"/>
+      <c r="C265" s="23"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="B266" s="63"/>
-      <c r="C266" s="26"/>
+      <c r="C266" s="23"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="B267" s="63"/>
-      <c r="C267" s="26"/>
+      <c r="C267" s="23"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="B268" s="63"/>
-      <c r="C268" s="26"/>
+      <c r="C268" s="23"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="B269" s="63"/>
-      <c r="C269" s="26"/>
+      <c r="C269" s="23"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="B270" s="63"/>
-      <c r="C270" s="26"/>
+      <c r="C270" s="23"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="B271" s="63"/>
-      <c r="C271" s="26"/>
+      <c r="C271" s="23"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="B272" s="63"/>
-      <c r="C272" s="26"/>
+      <c r="C272" s="23"/>
     </row>
     <row r="273" ht="14.25" customHeight="1"/>
     <row r="274" ht="14.25" customHeight="1"/>
@@ -9658,362 +9655,362 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="2" ht="15.0" customHeight="1">
-      <c r="A2" s="7"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="11"/>
     </row>
     <row r="3" ht="37.5" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" ht="39.75" customHeight="1">
-      <c r="A5" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="20" t="s">
+      <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="C5" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>21</v>
+      <c r="D5" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="23">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="A6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="23">
         <v>27.0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="23" t="s">
+      <c r="A7" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="23">
-        <v>2.0</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="E7" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="23">
         <v>32.0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="F8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="23">
         <v>31.0</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="23">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="26">
-        <v>90.0</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="23" t="s">
+      <c r="B11" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="23" t="s">
+      <c r="B12" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="23">
-        <v>6.0</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="B14" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="23">
-        <v>7.0</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="23" t="s">
+      <c r="C15" s="21">
+        <v>10.0</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="23">
-        <v>8.0</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="23" t="s">
+      <c r="C16" s="21">
+        <v>11.0</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="23">
-        <v>9.0</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="23" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="23" t="s">
+      <c r="B20" s="29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B21" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="23">
-        <v>11.0</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="32" t="s">
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="34" t="s">
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="s">
+      <c r="B23" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="26" t="s">
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="36" t="s">
+      <c r="B24" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="36"/>
-      <c r="B25" s="26"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="23"/>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -10992,104 +10989,104 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="10"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>5</v>
+      <c r="A2" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1"/>
     <row r="4" ht="33.75" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="33.75" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="19" t="s">
+    </row>
+    <row r="6" ht="33.75" customHeight="1">
+      <c r="A6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" ht="33.75" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="B7" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="33.75" customHeight="1">
+      <c r="A8" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="33.75" customHeight="1">
+      <c r="A9" s="16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="B9" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="33.75" customHeight="1">
+      <c r="A10" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="33.75" customHeight="1">
+      <c r="A11" s="16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" ht="33.75" customHeight="1">
-      <c r="A8" s="19" t="s">
+      <c r="B11" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="33.75" customHeight="1">
+      <c r="A12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B12" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" ht="33.75" customHeight="1">
+      <c r="A13" s="16" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" ht="33.75" customHeight="1">
-      <c r="A9" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="B13" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="33.75" customHeight="1">
-      <c r="A10" s="19" t="s">
+    <row r="14" ht="33.75" customHeight="1">
+      <c r="A14" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B14" s="16" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="11" ht="33.75" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" ht="33.75" customHeight="1">
-      <c r="A12" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" ht="33.75" customHeight="1">
-      <c r="A13" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" ht="33.75" customHeight="1">
-      <c r="A14" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1"/>
